--- a/R/Outputs/species_results.xlsx
+++ b/R/Outputs/species_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucascamacho/Dropbox/Doc/Code/evowm/R/Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0680C24-5064-BC40-BB95-62AF6F814F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EE6302-59A8-2C49-A9C7-B2E26E4D1D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{E18D1DED-CB54-0344-A455-D5933AF2B419}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="152">
   <si>
     <t>Predictor</t>
   </si>
@@ -459,6 +459,39 @@
   </si>
   <si>
     <t>9.49</t>
+  </si>
+  <si>
+    <t>Adjusted p (FDR)</t>
+  </si>
+  <si>
+    <t>0.0828</t>
+  </si>
+  <si>
+    <t>0.1913</t>
+  </si>
+  <si>
+    <t>0.8900</t>
+  </si>
+  <si>
+    <t>0.2908</t>
+  </si>
+  <si>
+    <t>0.5520</t>
+  </si>
+  <si>
+    <t>0.0180</t>
+  </si>
+  <si>
+    <t>0.5738</t>
+  </si>
+  <si>
+    <t>0.2340</t>
+  </si>
+  <si>
+    <t>0.2000</t>
+  </si>
+  <si>
+    <t>0.7412</t>
   </si>
 </sst>
 </file>
@@ -511,7 +544,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -653,11 +686,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -725,6 +769,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1061,10 +1111,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53C8BFA-3700-8548-9ECA-B01F5122F735}">
-  <dimension ref="E6:X30"/>
+  <dimension ref="B6:X30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
     <col min="20" max="20" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -1072,12 +1123,12 @@
     <col min="24" max="24" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="5:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="M6" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="5:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
       <c r="I7" s="9" t="s">
         <v>49</v>
       </c>
@@ -1103,15 +1154,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E8" s="9" t="s">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B8" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="C8" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="D8" s="17" t="s">
         <v>2</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>0</v>
@@ -1146,12 +1200,13 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E9" s="20" t="s">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B9" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24"/>
       <c r="I9" s="20" t="s">
         <v>55</v>
       </c>
@@ -1183,15 +1238,18 @@
       <c r="W9" s="20"/>
       <c r="X9" s="20"/>
     </row>
-    <row r="10" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E10" s="1" t="s">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="C10" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>51</v>
@@ -1236,15 +1294,18 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E11" s="1" t="s">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="C11" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>9</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>52</v>
@@ -1271,15 +1332,18 @@
       <c r="W11" s="23"/>
       <c r="X11" s="24"/>
     </row>
-    <row r="12" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E12" s="1" t="s">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="C12" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>53</v>
@@ -1324,15 +1388,18 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E13" s="1" t="s">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="C13" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>54</v>
@@ -1377,15 +1444,18 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E14" s="1" t="s">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="C14" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21"/>
@@ -1424,15 +1494,18 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E15" s="1" t="s">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="C15" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>32</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>51</v>
@@ -1468,15 +1541,18 @@
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="5:24" x14ac:dyDescent="0.2">
-      <c r="E16" s="1" t="s">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="C16" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>37</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="T16" s="6" t="s">
         <v>52</v>
@@ -1494,29 +1570,35 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E17" s="1" t="s">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="C17" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>42</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="M17" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E18" s="1" t="s">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="C18" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>24</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I18" s="2"/>
       <c r="M18" s="9" t="s">
@@ -1535,12 +1617,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E19" s="20" t="s">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
       <c r="M19" s="10" t="s">
         <v>95</v>
       </c>
@@ -1557,15 +1640,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E20" s="1" t="s">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="C20" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>6</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>51</v>
@@ -1583,15 +1669,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E21" s="1" t="s">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="C21" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>52</v>
@@ -1609,15 +1698,18 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E22" s="1" t="s">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="C22" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>18</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>53</v>
@@ -1635,15 +1727,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E23" s="1" t="s">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="C23" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>24</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>54</v>
@@ -1661,15 +1756,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E24" s="1" t="s">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="C24" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>29</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>96</v>
@@ -1687,65 +1785,77 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E25" s="1" t="s">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="C25" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E26" s="1" t="s">
+      <c r="E25" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="C26" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="27" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E27" s="1" t="s">
+      <c r="E26" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="C27" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="28" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E28" s="6" t="s">
+      <c r="E27" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B28" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="D28" s="8" t="s">
         <v>48</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>151</v>
       </c>
       <c r="J28" s="2"/>
       <c r="R28" s="18"/>
     </row>
-    <row r="30" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="R30" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I14:K14"/>
     <mergeCell ref="M8:R8"/>
     <mergeCell ref="M11:R11"/>
     <mergeCell ref="T11:X11"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/R/Outputs/species_results.xlsx
+++ b/R/Outputs/species_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucascamacho/Dropbox/Doc/Code/evowm/R/Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EE6302-59A8-2C49-A9C7-B2E26E4D1D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03476F2A-8E6F-C54A-974F-72F418D4D2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{E18D1DED-CB54-0344-A455-D5933AF2B419}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="171">
   <si>
     <t>Predictor</t>
   </si>
@@ -419,15 +419,6 @@
     <t>0.75</t>
   </si>
   <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>3367.735</t>
-  </si>
-  <si>
-    <t>0.0002</t>
-  </si>
-  <si>
     <t>Rate of Adaptation</t>
   </si>
   <si>
@@ -492,13 +483,79 @@
   </si>
   <si>
     <t>0.7412</t>
+  </si>
+  <si>
+    <t>OU models slopes and SE</t>
+  </si>
+  <si>
+    <t>Predictors</t>
+  </si>
+  <si>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>Integration + Size + NMDS1 + NMDS2</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>8674.481</t>
+  </si>
+  <si>
+    <t>0.00079</t>
+  </si>
+  <si>
+    <t>-4.94</t>
+  </si>
+  <si>
+    <t>-4.06</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>0.00021</t>
+  </si>
+  <si>
+    <t>3186.782</t>
+  </si>
+  <si>
+    <t>2855.007</t>
+  </si>
+  <si>
+    <t>0.00024</t>
+  </si>
+  <si>
+    <t>-0.48 ± 0.062</t>
+  </si>
+  <si>
+    <t>-0.077 ± 0.046</t>
+  </si>
+  <si>
+    <t>-0.14 ± 0.091</t>
+  </si>
+  <si>
+    <t>-0.12 ± 0.073</t>
+  </si>
+  <si>
+    <t>-0.43 ± 0.062</t>
+  </si>
+  <si>
+    <t>-0.055 ± 0.025</t>
+  </si>
+  <si>
+    <t>-0.025 ± 0.031</t>
+  </si>
+  <si>
+    <t>-0.029 ± 0.026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -535,6 +592,12 @@
       <name val="Cambria Math"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -701,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -756,25 +819,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1111,24 +1249,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53C8BFA-3700-8548-9ECA-B01F5122F735}">
-  <dimension ref="B6:X30"/>
+  <dimension ref="B6:AE30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:31" x14ac:dyDescent="0.2">
       <c r="M6" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:31" x14ac:dyDescent="0.2">
       <c r="I7" s="9" t="s">
         <v>49</v>
       </c>
@@ -1153,8 +1295,16 @@
       <c r="T7" s="9" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Z7" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+    </row>
+    <row r="8" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B8" s="17" t="s">
         <v>0</v>
       </c>
@@ -1164,8 +1314,8 @@
       <c r="D8" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>141</v>
+      <c r="E8" s="20" t="s">
+        <v>138</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>0</v>
@@ -1176,14 +1326,14 @@
       <c r="K8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="20" t="s">
+      <c r="M8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
       <c r="T8" s="13" t="s">
         <v>61</v>
       </c>
@@ -1194,24 +1344,34 @@
         <v>63</v>
       </c>
       <c r="W8" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="X8" s="13" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+      <c r="Z8" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA8" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB8" s="21"/>
+      <c r="AC8" s="21"/>
+      <c r="AD8" s="21"/>
+      <c r="AE8" s="21"/>
+    </row>
+    <row r="9" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B9" s="22" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
       <c r="E9" s="24"/>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
       <c r="M9" s="1" t="s">
         <v>66</v>
       </c>
@@ -1230,26 +1390,34 @@
       <c r="R9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="T9" s="20" t="s">
+      <c r="T9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-    </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB9" s="21"/>
+      <c r="AC9" s="21"/>
+      <c r="AD9" s="21"/>
+      <c r="AE9" s="21"/>
+    </row>
+    <row r="10" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>51</v>
@@ -1282,30 +1450,38 @@
         <v>51</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="V10" s="2">
         <v>0</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB10" s="44"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="12"/>
+      <c r="AE10" s="32"/>
+    </row>
+    <row r="11" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>52</v>
@@ -1316,14 +1492,14 @@
       <c r="K11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="20" t="s">
+      <c r="M11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
       <c r="T11" s="22" t="s">
         <v>7</v>
       </c>
@@ -1331,19 +1507,29 @@
       <c r="V11" s="23"/>
       <c r="W11" s="23"/>
       <c r="X11" s="24"/>
-    </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Z11" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA11" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="34"/>
+      <c r="AD11" s="34"/>
+      <c r="AE11" s="4"/>
+    </row>
+    <row r="12" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>53</v>
@@ -1382,24 +1568,34 @@
         <v>0</v>
       </c>
       <c r="W12" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="X12" s="19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+      <c r="Z12" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA12" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="34"/>
+      <c r="AD12" s="34"/>
+      <c r="AE12" s="4"/>
+    </row>
+    <row r="13" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>54</v>
@@ -1438,28 +1634,38 @@
         <v>123</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="Z13" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA13" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="34"/>
+      <c r="AD13" s="34"/>
+      <c r="AE13" s="4"/>
+    </row>
+    <row r="14" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
+        <v>139</v>
+      </c>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
       <c r="M14" s="1" t="s">
         <v>54</v>
       </c>
@@ -1488,24 +1694,34 @@
         <v>124</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="Z14" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA14" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="34"/>
+      <c r="AD14" s="34"/>
+      <c r="AE14" s="4"/>
+    </row>
+    <row r="15" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>51</v>
@@ -1535,24 +1751,32 @@
         <v>125</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB15" s="21"/>
+      <c r="AC15" s="42"/>
+      <c r="AD15" s="21"/>
+      <c r="AE15" s="21"/>
+    </row>
+    <row r="16" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="T16" s="6" t="s">
         <v>52</v>
@@ -1564,41 +1788,82 @@
         <v>126</v>
       </c>
       <c r="W16" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="X16" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB16" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC16" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD16" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE16" s="38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M17" s="17" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T17" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="24"/>
+      <c r="Z17" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA17" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB17" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC17" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD17" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE17" s="39" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2"/>
       <c r="M18" s="9" t="s">
@@ -1616,8 +1881,41 @@
       <c r="Q18" s="9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T18" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="U18" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="V18" s="12">
+        <v>0</v>
+      </c>
+      <c r="W18" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="X18" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z18" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA18" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB18" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC18" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD18" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE18" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B19" s="22" t="s">
         <v>7</v>
       </c>
@@ -1639,19 +1937,52 @@
       <c r="Q19" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T19" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="U19" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="V19" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="W19" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="X19" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z19" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA19" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB19" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC19" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD19" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE19" s="39" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>51</v>
@@ -1668,19 +1999,37 @@
       <c r="Q20" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Z20" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA20" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB20" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC20" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD20" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE20" s="39" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>52</v>
@@ -1697,19 +2046,27 @@
       <c r="Q21" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB21" s="21"/>
+      <c r="AC21" s="21"/>
+      <c r="AD21" s="21"/>
+      <c r="AE21" s="21"/>
+    </row>
+    <row r="22" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>53</v>
@@ -1726,19 +2083,29 @@
       <c r="Q22" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB22" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="4"/>
+    </row>
+    <row r="23" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>54</v>
@@ -1755,19 +2122,29 @@
       <c r="Q23" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Z23" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA23" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB23" s="36"/>
+      <c r="AC23" s="34"/>
+      <c r="AD23" s="34"/>
+      <c r="AE23" s="4"/>
+    </row>
+    <row r="24" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>96</v>
@@ -1784,50 +2161,86 @@
       <c r="Q24" s="8" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Z24" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA24" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB24" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC24" s="34"/>
+      <c r="AD24" s="34"/>
+      <c r="AE24" s="4"/>
+    </row>
+    <row r="25" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+      <c r="Z25" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA25" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB25" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC25" s="34"/>
+      <c r="AD25" s="34"/>
+      <c r="AE25" s="4"/>
+    </row>
+    <row r="26" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+      <c r="Z26" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA26" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB26" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC26" s="7"/>
+      <c r="AD26" s="7"/>
+      <c r="AE26" s="8"/>
+    </row>
+    <row r="27" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B28" s="6" t="s">
         <v>46</v>
       </c>
@@ -1838,16 +2251,21 @@
         <v>48</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J28" s="2"/>
       <c r="R28" s="18"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:31" x14ac:dyDescent="0.2">
       <c r="R30" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
+    <mergeCell ref="Z7:AE7"/>
+    <mergeCell ref="AA9:AE9"/>
+    <mergeCell ref="AA15:AE15"/>
+    <mergeCell ref="AA21:AE21"/>
+    <mergeCell ref="AA8:AE8"/>
     <mergeCell ref="M8:R8"/>
     <mergeCell ref="M11:R11"/>
     <mergeCell ref="T11:X11"/>
@@ -1856,6 +2274,7 @@
     <mergeCell ref="T9:X9"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I14:K14"/>
+    <mergeCell ref="T17:X17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
